--- a/outputs/data_cleaned.xlsx
+++ b/outputs/data_cleaned.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t xml:space="preserve">patient_name</t>
   </si>
@@ -174,10 +174,19 @@
     <t xml:space="preserve">Data_Type.Phone.Number</t>
   </si>
   <si>
-    <t xml:space="preserve">Missing_Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Missing_Percent</t>
+    <t xml:space="preserve">Missing_Percent_Raw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing_Percent_Cleaned</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valid_Values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imputation</t>
   </si>
   <si>
     <t xml:space="preserve">Notes</t>
@@ -198,24 +207,60 @@
     <t xml:space="preserve">integer</t>
   </si>
   <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t xml:space="preserve">Age</t>
   </si>
   <si>
     <t xml:space="preserve">POSIXt</t>
   </si>
   <si>
+    <t xml:space="preserve">Patient age in years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0–120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median imputation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Converted from text where necessary</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gender</t>
   </si>
   <si>
+    <t xml:space="preserve">Patient gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Male, Female, Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standardised values</t>
+  </si>
+  <si>
     <t xml:space="preserve">Condition</t>
   </si>
   <si>
+    <t xml:space="preserve">Patient medical condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normalised to consistent format</t>
+  </si>
+  <si>
     <t xml:space="preserve">Medication</t>
   </si>
   <si>
     <t xml:space="preserve">Visit.Date</t>
   </si>
   <si>
+    <t xml:space="preserve">Date of patient visit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsed from multiple formats</t>
+  </si>
+  <si>
     <t xml:space="preserve">Blood.Pressure</t>
   </si>
   <si>
@@ -226,6 +271,12 @@
   </si>
   <si>
     <t xml:space="preserve">Phone.Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient contact number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-digit characters removed</t>
   </si>
 </sst>
 </file>
@@ -2132,40 +2183,49 @@
       <c r="N1" t="s">
         <v>55</v>
       </c>
+      <c r="O1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -2173,83 +2233,105 @@
       <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="N2"/>
+      <c r="N2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O2" t="s">
+        <v>64</v>
+      </c>
+      <c r="P2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
         <v>61</v>
       </c>
-      <c r="B3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" t="s">
-        <v>58</v>
-      </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>15.9</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3"/>
+      <c r="N3" t="s">
+        <v>67</v>
+      </c>
+      <c r="O3" t="s">
+        <v>68</v>
+      </c>
+      <c r="P3" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I4" t="s">
         <v>63</v>
       </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
-      </c>
-      <c r="G4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" t="s">
-        <v>60</v>
-      </c>
       <c r="J4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2257,41 +2339,52 @@
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4"/>
+      <c r="N4" t="s">
+        <v>72</v>
+      </c>
+      <c r="O4" t="s">
+        <v>73</v>
+      </c>
+      <c r="P4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I5" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2299,41 +2392,52 @@
       <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="N5"/>
+      <c r="N5" t="s">
+        <v>76</v>
+      </c>
+      <c r="O5" t="s">
+        <v>64</v>
+      </c>
+      <c r="P5" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -2341,41 +2445,52 @@
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6"/>
+      <c r="N6" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" t="s">
+        <v>64</v>
+      </c>
+      <c r="P6" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F7" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" t="s">
         <v>66</v>
       </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" t="s">
-        <v>57</v>
-      </c>
-      <c r="G7" t="s">
-        <v>62</v>
-      </c>
       <c r="H7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -2383,175 +2498,230 @@
       <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="N7"/>
+      <c r="N7" t="s">
+        <v>80</v>
+      </c>
+      <c r="O7" t="s">
+        <v>64</v>
+      </c>
+      <c r="P7" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>16.6</v>
       </c>
       <c r="M8" t="n">
         <v>14</v>
       </c>
-      <c r="N8"/>
+      <c r="N8" t="s">
+        <v>64</v>
+      </c>
+      <c r="O8" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L9" t="n">
-        <v>8</v>
+        <v>23.1</v>
       </c>
       <c r="M9" t="n">
         <v>16</v>
       </c>
-      <c r="N9"/>
+      <c r="N9" t="s">
+        <v>64</v>
+      </c>
+      <c r="O9" t="s">
+        <v>64</v>
+      </c>
+      <c r="P9" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L10" t="n">
-        <v>22</v>
+        <v>38.4</v>
       </c>
       <c r="M10" t="n">
         <v>44</v>
       </c>
-      <c r="N10"/>
+      <c r="N10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O10" t="s">
+        <v>64</v>
+      </c>
+      <c r="P10" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="I11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L11" t="n">
-        <v>21</v>
+        <v>17.9</v>
       </c>
       <c r="M11" t="n">
         <v>42</v>
       </c>
-      <c r="N11"/>
+      <c r="N11" t="s">
+        <v>86</v>
+      </c>
+      <c r="O11" t="s">
+        <v>64</v>
+      </c>
+      <c r="P11" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>87</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/data_cleaned.xlsx
+++ b/outputs/data_cleaned.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="98">
   <si>
     <t xml:space="preserve">patient_name</t>
   </si>
@@ -45,133 +45,112 @@
     <t xml:space="preserve">phone_number</t>
   </si>
   <si>
+    <t xml:space="preserve">age_original</t>
+  </si>
+  <si>
+    <t xml:space="preserve">age_imputed_flag</t>
+  </si>
+  <si>
     <t xml:space="preserve">david lee</t>
   </si>
   <si>
+    <t xml:space="preserve">Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heart Disease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metformin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">140/90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">name@hospital.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5555555555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emily davis</t>
+  </si>
+  <si>
     <t xml:space="preserve">Male</t>
   </si>
   <si>
+    <t xml:space="preserve">Diabetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120/80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">laura martinez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Asthma</t>
   </si>
   <si>
+    <t xml:space="preserve">110/70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact@domain.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">michael wilson</t>
+  </si>
+  <si>
     <t xml:space="preserve">Albuterol</t>
   </si>
   <si>
-    <t xml:space="preserve">110/70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name@hospital.org</t>
-  </si>
-  <si>
     <t xml:space="preserve">Female</t>
   </si>
   <si>
-    <t xml:space="preserve">None</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120/80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diabetes</t>
+    <t xml:space="preserve">mary clark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hypertension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">robert brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisinopril</t>
+  </si>
+  <si>
+    <t xml:space="preserve">patient@example.com</t>
   </si>
   <si>
     <t xml:space="preserve">Atorvastatin</t>
   </si>
   <si>
-    <t xml:space="preserve">140/90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heart Disease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metformin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5555555555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emily davis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypertension</t>
+    <t xml:space="preserve">130/85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1234567890</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sarah johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jane smith</t>
   </si>
   <si>
     <t xml:space="preserve">0987654321</t>
   </si>
   <si>
-    <t xml:space="preserve">1234567890</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact@domain.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisinopril</t>
+    <t xml:space="preserve">john doe</t>
   </si>
   <si>
     <t xml:space="preserve">james taylor</t>
   </si>
   <si>
-    <t xml:space="preserve">patient@example.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">jane smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130/85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">john doe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">laura martinez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mary clark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">michael wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">robert brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sarah johnson</t>
-  </si>
-  <si>
     <t xml:space="preserve">Variable_Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Data_Type.Patient.Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Type.Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Type.Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Type.Condition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Type.Medication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Type.Visit.Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Type.Blood.Pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Type.Cholesterol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Type.Email</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data_Type.Phone.Number</t>
+    <t xml:space="preserve">Data_Type</t>
   </si>
   <si>
     <t xml:space="preserve">Missing_Percent_Raw</t>
@@ -198,85 +177,136 @@
     <t xml:space="preserve">character</t>
   </si>
   <si>
+    <t xml:space="preserve">Patient Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See dataset documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Names standardised and deduplicated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age</t>
+  </si>
+  <si>
     <t xml:space="preserve">numeric</t>
   </si>
   <si>
+    <t xml:space="preserve">Patient Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0-120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Median imputation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text converted to numeric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patient Gender</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Male, Female, Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categorical values standardised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical Condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition names normalised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medication Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medication names standardised</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visit.Date</t>
+  </si>
+  <si>
     <t xml:space="preserve">POSIXct</t>
   </si>
   <si>
+    <t xml:space="preserve">Visit Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parsed from multiple date formats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood.Pressure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood Pressure Reading</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Cholesterol</t>
+  </si>
+  <si>
     <t xml:space="preserve">integer</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POSIXt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patient age in years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0–120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Median imputation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Converted from text where necessary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patient gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Male, Female, Other</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standardised values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patient medical condition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Normalised to consistent format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visit.Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date of patient visit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parsed from multiple formats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blood.Pressure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cholesterol</t>
+    <t xml:space="preserve">Cholesterol Level</t>
   </si>
   <si>
     <t xml:space="preserve">Email</t>
   </si>
   <si>
+    <t xml:space="preserve">Patient Email Address</t>
+  </si>
+  <si>
     <t xml:space="preserve">Phone.Number</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient contact number</t>
+    <t xml:space="preserve">Patient Contact Number</t>
   </si>
   <si>
     <t xml:space="preserve">Non-digit characters removed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age_Original</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Original Age Before Imputation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference variable only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stored for imputation comparison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age_Imputed_Flag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">logical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age Imputation Indicator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUE/FALSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated during imputation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicates imputed observations</t>
   </si>
 </sst>
 </file>
@@ -644,1099 +674,1319 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>43195</v>
+        <v>43845</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H2" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2"/>
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" t="n">
+        <v>25</v>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>43549</v>
+        <v>43195</v>
       </c>
       <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3"/>
+        <v>23</v>
+      </c>
+      <c r="H3" t="n">
+        <v>200</v>
+      </c>
       <c r="I3"/>
       <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F4" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="G4" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H4" t="n">
-        <v>220</v>
-      </c>
-      <c r="I4"/>
+        <v>160</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
       <c r="J4"/>
+      <c r="K4" t="n">
+        <v>35</v>
+      </c>
+      <c r="L4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>43845</v>
       </c>
       <c r="G5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" t="n">
-        <v>200</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H5"/>
       <c r="I5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="K5"/>
+      <c r="L5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" t="n">
         <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>43881</v>
       </c>
       <c r="G6" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H6" t="n">
         <v>180</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B7" t="n">
         <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>43195</v>
+        <v>43549</v>
       </c>
       <c r="G7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H7" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B8" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>43549</v>
+        <v>43881</v>
       </c>
       <c r="G8" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H8"/>
-      <c r="I8"/>
-      <c r="J8" t="s">
-        <v>28</v>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>43800</v>
+        <v>43845</v>
       </c>
       <c r="G9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H9" t="n">
         <v>180</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
-      </c>
-      <c r="J9" t="s">
-        <v>29</v>
+        <v>17</v>
+      </c>
+      <c r="J9"/>
+      <c r="K9" t="n">
+        <v>60</v>
+      </c>
+      <c r="L9" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>43881</v>
+      </c>
+      <c r="G10" t="s">
         <v>16</v>
       </c>
-      <c r="D10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>43845</v>
-      </c>
-      <c r="G10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10"/>
+      <c r="H10" t="n">
+        <v>220</v>
+      </c>
       <c r="I10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J10" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="K10" t="n">
+        <v>40</v>
+      </c>
+      <c r="L10" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B11" t="n">
         <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>43881</v>
       </c>
       <c r="G11" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H11" t="n">
-        <v>220</v>
-      </c>
-      <c r="I11"/>
-      <c r="J11" t="s">
-        <v>29</v>
+        <v>200</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>43195</v>
-      </c>
-      <c r="G12"/>
+        <v>43549</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
       <c r="H12" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="I12"/>
       <c r="J12" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="K12" t="n">
+        <v>40</v>
+      </c>
+      <c r="L12" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B13" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>43549</v>
       </c>
       <c r="G13" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" t="n">
-        <v>200</v>
-      </c>
-      <c r="I13"/>
-      <c r="J13" t="s">
-        <v>28</v>
+        <v>37</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13"/>
+      <c r="K13" t="n">
+        <v>25</v>
+      </c>
+      <c r="L13" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" t="n">
+        <v>70</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
         <v>32</v>
       </c>
-      <c r="B14" t="n">
-        <v>60</v>
-      </c>
-      <c r="C14" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" t="s">
-        <v>27</v>
-      </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>43800</v>
       </c>
-      <c r="G14"/>
+      <c r="G14" t="s">
+        <v>37</v>
+      </c>
       <c r="H14" t="n">
-        <v>200</v>
-      </c>
-      <c r="I14" t="s">
-        <v>33</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="I14"/>
       <c r="J14"/>
+      <c r="K14" t="n">
+        <v>70</v>
+      </c>
+      <c r="L14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>43845</v>
+        <v>43549</v>
       </c>
       <c r="G15" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H15" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="I15"/>
       <c r="J15" t="s">
-        <v>28</v>
+        <v>38</v>
+      </c>
+      <c r="K15" t="n">
+        <v>35</v>
+      </c>
+      <c r="L15" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B16" t="n">
         <v>60</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D16" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>43881</v>
       </c>
-      <c r="G16"/>
+      <c r="G16" t="s">
+        <v>23</v>
+      </c>
       <c r="H16" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I16"/>
-      <c r="J16" t="s">
-        <v>29</v>
+      <c r="J16"/>
+      <c r="K16" t="n">
+        <v>60</v>
+      </c>
+      <c r="L16" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B17" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E17" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>43195</v>
+        <v>43845</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
-      </c>
-      <c r="H17" t="n">
-        <v>200</v>
-      </c>
-      <c r="I17"/>
+        <v>23</v>
+      </c>
+      <c r="H17"/>
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
       <c r="J17" t="s">
-        <v>29</v>
+        <v>41</v>
+      </c>
+      <c r="K17" t="n">
+        <v>25</v>
+      </c>
+      <c r="L17" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B18" t="n">
         <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>43549</v>
       </c>
       <c r="G18" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="H18" t="n">
         <v>160</v>
       </c>
       <c r="I18" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J18"/>
+      <c r="K18" t="n">
+        <v>70</v>
+      </c>
+      <c r="L18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" t="n">
+        <v>35</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" t="s">
         <v>34</v>
       </c>
-      <c r="B19" t="n">
-        <v>40</v>
-      </c>
-      <c r="C19" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" t="s">
-        <v>24</v>
-      </c>
       <c r="F19" s="1" t="n">
-        <v>43800</v>
+        <v>43195</v>
       </c>
       <c r="G19" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="H19" t="n">
         <v>180</v>
       </c>
-      <c r="I19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J19" t="s">
-        <v>25</v>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19" t="n">
+        <v>35</v>
+      </c>
+      <c r="L19" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" t="n">
+        <v>25</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" t="s">
         <v>34</v>
-      </c>
-      <c r="B20" t="n">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>16</v>
-      </c>
-      <c r="D20" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" t="s">
-        <v>24</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>43845</v>
       </c>
       <c r="G20" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H20" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J20" t="s">
-        <v>29</v>
+        <v>41</v>
+      </c>
+      <c r="K20" t="n">
+        <v>25</v>
+      </c>
+      <c r="L20" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B21" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>43881</v>
+        <v>43800</v>
       </c>
       <c r="G21" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" t="n">
+        <v>220</v>
+      </c>
+      <c r="I21"/>
+      <c r="J21" t="s">
         <v>18</v>
       </c>
-      <c r="H21" t="n">
-        <v>200</v>
-      </c>
-      <c r="I21"/>
-      <c r="J21"/>
+      <c r="K21" t="n">
+        <v>70</v>
+      </c>
+      <c r="L21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B22" t="n">
         <v>60</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>43195</v>
       </c>
-      <c r="G22"/>
+      <c r="G22" t="s">
+        <v>23</v>
+      </c>
       <c r="H22" t="n">
-        <v>180</v>
-      </c>
-      <c r="I22" t="s">
-        <v>30</v>
-      </c>
-      <c r="J22"/>
+        <v>160</v>
+      </c>
+      <c r="I22"/>
+      <c r="J22" t="s">
+        <v>18</v>
+      </c>
+      <c r="K22" t="n">
+        <v>60</v>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="n">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
         <v>36</v>
       </c>
-      <c r="B23" t="n">
-        <v>70</v>
-      </c>
-      <c r="C23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" t="s">
-        <v>31</v>
-      </c>
       <c r="F23" s="1" t="n">
-        <v>43549</v>
+        <v>43881</v>
       </c>
       <c r="G23"/>
       <c r="H23" t="n">
         <v>220</v>
       </c>
-      <c r="I23" t="s">
-        <v>30</v>
-      </c>
+      <c r="I23"/>
       <c r="J23" t="s">
-        <v>28</v>
+        <v>38</v>
+      </c>
+      <c r="K23" t="n">
+        <v>60</v>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B24" t="n">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" t="s">
         <v>36</v>
       </c>
-      <c r="B24" t="n">
-        <v>25</v>
-      </c>
-      <c r="C24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="F24" s="1" t="n">
+        <v>43881</v>
+      </c>
+      <c r="G24" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" t="n">
+        <v>200</v>
+      </c>
+      <c r="I24" t="s">
         <v>27</v>
       </c>
-      <c r="E24" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>43800</v>
-      </c>
-      <c r="G24"/>
-      <c r="H24" t="n">
-        <v>180</v>
-      </c>
-      <c r="I24"/>
-      <c r="J24" t="s">
-        <v>28</v>
+      <c r="J24"/>
+      <c r="K24" t="n">
+        <v>40</v>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B25" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E25" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>43845</v>
+        <v>43881</v>
       </c>
       <c r="G25" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H25" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="I25" t="s">
-        <v>30</v>
-      </c>
-      <c r="J25" t="s">
-        <v>28</v>
+        <v>17</v>
+      </c>
+      <c r="J25"/>
+      <c r="K25" t="n">
+        <v>70</v>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B26" t="n">
         <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D26" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>43195</v>
+      </c>
+      <c r="G26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" t="n">
+        <v>220</v>
+      </c>
+      <c r="I26" t="s">
         <v>27</v>
       </c>
-      <c r="E26" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>43881</v>
-      </c>
-      <c r="G26" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" t="n">
-        <v>200</v>
-      </c>
-      <c r="I26" t="s">
-        <v>30</v>
-      </c>
-      <c r="J26"/>
+      <c r="J26" t="s">
+        <v>41</v>
+      </c>
+      <c r="K26"/>
+      <c r="L26" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="B27" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>43195</v>
       </c>
       <c r="G27" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H27" t="n">
         <v>220</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="J27"/>
+      <c r="K27" t="n">
+        <v>70</v>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B28" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>43549</v>
+        <v>43845</v>
       </c>
       <c r="G28" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H28" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="I28"/>
       <c r="J28" t="s">
-        <v>29</v>
+        <v>41</v>
+      </c>
+      <c r="K28" t="n">
+        <v>25</v>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B29" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>43800</v>
+        <v>43845</v>
       </c>
       <c r="G29" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H29" t="n">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="I29" t="s">
-        <v>30</v>
-      </c>
-      <c r="J29"/>
+        <v>27</v>
+      </c>
+      <c r="J29" t="s">
+        <v>41</v>
+      </c>
+      <c r="K29" t="n">
+        <v>70</v>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="B30" t="n">
         <v>60</v>
       </c>
       <c r="C30" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E30" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>43845</v>
+        <v>43800</v>
       </c>
       <c r="G30" t="s">
-        <v>21</v>
-      </c>
-      <c r="H30" t="n">
-        <v>180</v>
-      </c>
-      <c r="I30" t="s">
-        <v>15</v>
-      </c>
-      <c r="J30"/>
+        <v>16</v>
+      </c>
+      <c r="H30"/>
+      <c r="I30"/>
+      <c r="J30" t="s">
+        <v>38</v>
+      </c>
+      <c r="K30" t="n">
+        <v>60</v>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B31" t="n">
         <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D31" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>43881</v>
+        <v>43845</v>
       </c>
       <c r="G31" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H31" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="I31" t="s">
-        <v>15</v>
-      </c>
-      <c r="J31"/>
+        <v>27</v>
+      </c>
+      <c r="J31" t="s">
+        <v>38</v>
+      </c>
+      <c r="K31"/>
+      <c r="L31" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B32" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>43195</v>
+        <v>43800</v>
       </c>
       <c r="G32"/>
       <c r="H32" t="n">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
-      </c>
-      <c r="J32" t="s">
-        <v>29</v>
+        <v>35</v>
+      </c>
+      <c r="J32"/>
+      <c r="K32" t="n">
+        <v>60</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B33" t="n">
         <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E33" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>43549</v>
+        <v>43800</v>
       </c>
       <c r="G33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H33" t="n">
         <v>180</v>
       </c>
-      <c r="I33"/>
-      <c r="J33"/>
+      <c r="I33" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" t="s">
+        <v>18</v>
+      </c>
+      <c r="K33" t="n">
+        <v>40</v>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B34" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>43845</v>
+      </c>
+      <c r="G34" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" t="n">
+        <v>180</v>
+      </c>
+      <c r="I34" t="s">
         <v>17</v>
       </c>
-      <c r="F34" s="1" t="n">
-        <v>43800</v>
-      </c>
-      <c r="G34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H34" t="n">
-        <v>220</v>
-      </c>
-      <c r="I34"/>
       <c r="J34" t="s">
-        <v>25</v>
+        <v>41</v>
+      </c>
+      <c r="K34" t="n">
+        <v>25</v>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" t="n">
+        <v>35</v>
+      </c>
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>43195</v>
+      </c>
+      <c r="G35"/>
+      <c r="H35" t="n">
+        <v>200</v>
+      </c>
+      <c r="I35"/>
+      <c r="J35" t="s">
         <v>38</v>
       </c>
-      <c r="B35" t="n">
-        <v>25</v>
-      </c>
-      <c r="C35" t="s">
-        <v>22</v>
-      </c>
-      <c r="D35" t="s">
-        <v>23</v>
-      </c>
-      <c r="E35" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>43845</v>
-      </c>
-      <c r="G35" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" t="n">
-        <v>180</v>
-      </c>
-      <c r="I35" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" t="s">
-        <v>28</v>
+      <c r="K35" t="n">
+        <v>35</v>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" t="n">
+        <v>40</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>43800</v>
+      </c>
+      <c r="G36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H36" t="n">
+        <v>180</v>
+      </c>
+      <c r="I36" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" t="s">
         <v>38</v>
       </c>
-      <c r="B36" t="n">
-        <v>70</v>
-      </c>
-      <c r="C36" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" t="s">
-        <v>23</v>
-      </c>
-      <c r="E36" t="s">
-        <v>24</v>
-      </c>
-      <c r="F36" s="1" t="n">
-        <v>43881</v>
-      </c>
-      <c r="G36" t="s">
-        <v>35</v>
-      </c>
-      <c r="H36" t="n">
-        <v>160</v>
-      </c>
-      <c r="I36" t="s">
-        <v>15</v>
-      </c>
-      <c r="J36"/>
+      <c r="K36" t="n">
+        <v>40</v>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" t="n">
         <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E37" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F37" s="1" t="n">
         <v>43195</v>
       </c>
       <c r="G37" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="H37" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="I37"/>
-      <c r="J37"/>
+      <c r="J37" t="s">
+        <v>38</v>
+      </c>
+      <c r="K37" t="n">
+        <v>35</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C38" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F38" s="1" t="n">
         <v>43549</v>
       </c>
       <c r="G38" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H38" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="I38"/>
       <c r="J38" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="K38"/>
+      <c r="L38" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1744,390 +1994,454 @@
         <v>39</v>
       </c>
       <c r="B39" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="C39" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D39" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>43800</v>
+        <v>43881</v>
       </c>
       <c r="G39" t="s">
-        <v>21</v>
-      </c>
-      <c r="H39"/>
-      <c r="I39"/>
-      <c r="J39" t="s">
-        <v>29</v>
+        <v>37</v>
+      </c>
+      <c r="H39" t="n">
+        <v>200</v>
+      </c>
+      <c r="I39" t="s">
+        <v>27</v>
+      </c>
+      <c r="J39"/>
+      <c r="K39" t="n">
+        <v>35</v>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B40" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D40" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E40" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>43845</v>
+        <v>43549</v>
       </c>
       <c r="G40" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H40"/>
-      <c r="I40" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" t="s">
-        <v>25</v>
+      <c r="I40"/>
+      <c r="J40"/>
+      <c r="K40" t="n">
+        <v>35</v>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C41" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D41" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E41" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>43881</v>
-      </c>
-      <c r="G41" t="s">
-        <v>21</v>
-      </c>
+        <v>43800</v>
+      </c>
+      <c r="G41"/>
       <c r="H41" t="n">
-        <v>220</v>
-      </c>
-      <c r="I41" t="s">
-        <v>33</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="I41"/>
       <c r="J41" t="s">
-        <v>25</v>
+        <v>41</v>
+      </c>
+      <c r="K41" t="n">
+        <v>25</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B42" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D42" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E42" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F42" s="1" t="n">
         <v>43195</v>
       </c>
-      <c r="G42" t="s">
-        <v>14</v>
-      </c>
+      <c r="G42"/>
       <c r="H42" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="I42" t="s">
-        <v>30</v>
-      </c>
-      <c r="J42" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="J42"/>
+      <c r="K42" t="n">
+        <v>60</v>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B43" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C43" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E43" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>43549</v>
+        <v>43195</v>
       </c>
       <c r="G43" t="s">
+        <v>37</v>
+      </c>
+      <c r="H43" t="n">
+        <v>220</v>
+      </c>
+      <c r="I43" t="s">
         <v>35</v>
       </c>
-      <c r="H43"/>
-      <c r="I43" t="s">
-        <v>15</v>
-      </c>
       <c r="J43"/>
+      <c r="K43" t="n">
+        <v>35</v>
+      </c>
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="B44" t="n">
         <v>35</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E44" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F44" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="G44" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H44" t="n">
         <v>220</v>
       </c>
       <c r="I44" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J44" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="K44" t="n">
+        <v>35</v>
+      </c>
+      <c r="L44" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B45" t="n">
         <v>70</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E45" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>43845</v>
-      </c>
-      <c r="G45" t="s">
-        <v>21</v>
-      </c>
+        <v>43549</v>
+      </c>
+      <c r="G45"/>
       <c r="H45" t="n">
         <v>220</v>
       </c>
       <c r="I45" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J45" t="s">
-        <v>28</v>
+        <v>41</v>
+      </c>
+      <c r="K45" t="n">
+        <v>70</v>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="B46" t="n">
         <v>40</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D46" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>43881</v>
+        <v>43800</v>
       </c>
       <c r="G46" t="s">
-        <v>18</v>
-      </c>
-      <c r="H46"/>
-      <c r="I46" t="s">
-        <v>15</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="H46" t="n">
+        <v>220</v>
+      </c>
+      <c r="I46"/>
       <c r="J46"/>
+      <c r="K46" t="n">
+        <v>40</v>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B47" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D47" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E47" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>43195</v>
+        <v>43845</v>
       </c>
       <c r="G47" t="s">
-        <v>18</v>
-      </c>
-      <c r="H47" t="n">
-        <v>160</v>
-      </c>
-      <c r="I47"/>
+        <v>26</v>
+      </c>
+      <c r="H47"/>
+      <c r="I47" t="s">
+        <v>27</v>
+      </c>
       <c r="J47" t="s">
-        <v>25</v>
+        <v>38</v>
+      </c>
+      <c r="K47" t="n">
+        <v>25</v>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B48" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C48" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D48" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E48" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F48" s="1" t="n">
         <v>43549</v>
       </c>
       <c r="G48" t="s">
-        <v>21</v>
-      </c>
-      <c r="H48" t="n">
-        <v>160</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H48"/>
       <c r="I48"/>
       <c r="J48" t="s">
-        <v>25</v>
+        <v>41</v>
+      </c>
+      <c r="K48" t="n">
+        <v>35</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" t="n">
+        <v>60</v>
+      </c>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D49" t="s">
+        <v>21</v>
+      </c>
+      <c r="E49" t="s">
+        <v>36</v>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>43549</v>
+      </c>
+      <c r="G49" t="s">
+        <v>16</v>
+      </c>
+      <c r="H49" t="n">
+        <v>200</v>
+      </c>
+      <c r="I49"/>
+      <c r="J49" t="s">
         <v>41</v>
       </c>
-      <c r="B49" t="n">
-        <v>70</v>
-      </c>
-      <c r="C49" t="s">
-        <v>16</v>
-      </c>
-      <c r="D49" t="s">
-        <v>27</v>
-      </c>
-      <c r="E49" t="s">
-        <v>13</v>
-      </c>
-      <c r="F49" s="1" t="n">
-        <v>43800</v>
-      </c>
-      <c r="G49" t="s">
-        <v>35</v>
-      </c>
-      <c r="H49" t="n">
-        <v>220</v>
-      </c>
-      <c r="I49"/>
-      <c r="J49"/>
+      <c r="K49" t="n">
+        <v>60</v>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B50" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C50" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" t="s">
         <v>22</v>
       </c>
-      <c r="D50" t="s">
-        <v>19</v>
-      </c>
       <c r="E50" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>43845</v>
-      </c>
-      <c r="G50" t="s">
-        <v>18</v>
-      </c>
-      <c r="H50"/>
+        <v>43195</v>
+      </c>
+      <c r="G50"/>
+      <c r="H50" t="n">
+        <v>160</v>
+      </c>
       <c r="I50" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J50" t="s">
-        <v>28</v>
+        <v>38</v>
+      </c>
+      <c r="K50"/>
+      <c r="L50" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="B51" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C51" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E51" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F51" s="1" t="n">
         <v>43881</v>
       </c>
       <c r="G51" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="H51" t="n">
-        <v>200</v>
-      </c>
-      <c r="I51" t="s">
-        <v>30</v>
-      </c>
-      <c r="J51"/>
+        <v>220</v>
+      </c>
+      <c r="I51"/>
+      <c r="J51" t="s">
+        <v>38</v>
+      </c>
+      <c r="K51"/>
+      <c r="L51" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2142,532 +2456,262 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H1" t="s">
-        <v>49</v>
-      </c>
-      <c r="I1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J1" t="s">
         <v>51</v>
-      </c>
-      <c r="K1" t="s">
-        <v>52</v>
-      </c>
-      <c r="L1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="H2" t="s">
-        <v>60</v>
-      </c>
-      <c r="I2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>64</v>
-      </c>
-      <c r="O2" t="s">
-        <v>64</v>
-      </c>
-      <c r="P2" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D3" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="C3" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
         <v>60</v>
       </c>
       <c r="G3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H3" t="s">
-        <v>60</v>
-      </c>
-      <c r="I3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>67</v>
-      </c>
-      <c r="O3" t="s">
-        <v>68</v>
-      </c>
-      <c r="P3" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" t="s">
-        <v>63</v>
-      </c>
-      <c r="J4" t="s">
-        <v>60</v>
-      </c>
-      <c r="K4" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>72</v>
-      </c>
-      <c r="O4" t="s">
-        <v>73</v>
-      </c>
-      <c r="P4" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" t="s">
-        <v>63</v>
-      </c>
-      <c r="J5" t="s">
-        <v>60</v>
-      </c>
-      <c r="K5" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>76</v>
-      </c>
-      <c r="O5" t="s">
-        <v>64</v>
-      </c>
-      <c r="P5" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>60</v>
-      </c>
-      <c r="I6" t="s">
-        <v>63</v>
-      </c>
-      <c r="J6" t="s">
-        <v>60</v>
-      </c>
-      <c r="K6" t="s">
-        <v>60</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>64</v>
-      </c>
-      <c r="O6" t="s">
-        <v>64</v>
-      </c>
-      <c r="P6" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" t="s">
-        <v>60</v>
+        <v>74</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G7" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="H7" t="s">
-        <v>60</v>
-      </c>
-      <c r="I7" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" t="s">
-        <v>60</v>
-      </c>
-      <c r="K7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>80</v>
-      </c>
-      <c r="O7" t="s">
-        <v>64</v>
-      </c>
-      <c r="P7" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="C8" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="H8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I8" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" t="s">
-        <v>60</v>
-      </c>
-      <c r="K8" t="s">
-        <v>60</v>
-      </c>
-      <c r="L8" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="M8" t="n">
-        <v>14</v>
-      </c>
-      <c r="N8" t="s">
-        <v>64</v>
-      </c>
-      <c r="O8" t="s">
-        <v>64</v>
-      </c>
-      <c r="P8" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C9" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" t="s">
-        <v>60</v>
+        <v>81</v>
+      </c>
+      <c r="C9" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>16</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
-      </c>
-      <c r="I9" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" t="s">
-        <v>60</v>
-      </c>
-      <c r="L9" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>16</v>
-      </c>
-      <c r="N9" t="s">
-        <v>64</v>
-      </c>
-      <c r="O9" t="s">
-        <v>64</v>
-      </c>
-      <c r="P9" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
         <v>84</v>
       </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" t="s">
-        <v>60</v>
-      </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>62</v>
+        <v>22</v>
       </c>
       <c r="H10" t="s">
-        <v>60</v>
-      </c>
-      <c r="I10" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" t="s">
-        <v>60</v>
-      </c>
-      <c r="K10" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="M10" t="n">
-        <v>44</v>
-      </c>
-      <c r="N10" t="s">
-        <v>64</v>
-      </c>
-      <c r="O10" t="s">
-        <v>64</v>
-      </c>
-      <c r="P10" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -2675,52 +2719,73 @@
         <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" t="s">
-        <v>60</v>
+        <v>53</v>
+      </c>
+      <c r="C11" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="H11" t="s">
-        <v>60</v>
-      </c>
-      <c r="I11" t="s">
-        <v>63</v>
-      </c>
-      <c r="J11" t="s">
-        <v>60</v>
-      </c>
-      <c r="K11" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" t="n">
-        <v>17.9</v>
-      </c>
-      <c r="M11" t="n">
-        <v>42</v>
-      </c>
-      <c r="N11" t="s">
-        <v>86</v>
-      </c>
-      <c r="O11" t="s">
-        <v>64</v>
-      </c>
-      <c r="P11" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q11" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12"/>
+      <c r="D12" t="n">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>89</v>
+      </c>
+      <c r="F12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13"/>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" t="s">
+        <v>96</v>
+      </c>
+      <c r="H13" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
